--- a/leads/austrian_dental_leads.xlsx
+++ b/leads/austrian_dental_leads.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dental Practice Leads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top 10 Priority" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Top 10 Easy Wins" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="High Priority (by City)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dental Practice Leads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top 10 Priority" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Top 10 Easy Wins" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary Analysis" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,20 +111,20 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -499,6 +500,2246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="65" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Practice Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dentist Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Main Weakness</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Detailed Observation</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Online Booking</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mobile Friendly</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Personalized Outreach Hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Viktor M. Ribisch</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Viktor M. Ribisch</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Linz</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>http://www.zahnarzt-ribisch.at/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>zahnarzt@ribisch.at</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>+43 732 90 10 22 00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS - site served over insecure HTTP</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Wahlarzt practice offering aesthetic dentistry, implantology and invisible braces. Website served over plain HTTP with no SSL encryption. No online booking - phone only. Modern services advertised but the site itself signals neglect.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website läuft ohne HTTPS - Browser zeigen Patienten eine Sicherheitswarnung, gerade bei Premium-Leistungen wie unsichtbarer Zahnspange ein Vertrauensverlust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Rintelen</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Rintelen</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Linz</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>http://dr-rintelen.at/</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>+43 732 65 33 40</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and very old CMS</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only site built on an outdated CMS (content paths like /content/e22738/e22739). Old logo image structure indicates the site has not been rebuilt in many years. No online booking.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website basiert auf einem veralteten Content-System ohne HTTPS - ein moderner Neuaufbau würde Ladezeit, Sicherheit und Auffindbarkeit deutlich verbessern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Heinz-Dieter Müller</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Heinz-Dieter Müller PhD</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Linz</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>http://zahnarzt-mueller-linz.at/</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>+43 732 302066</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and minimal content</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only implantology practice. Minimal content visible - essentially just a phone number. No modern features, no online booking, no team presentation.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Implantologie-Praxis hat online kaum Sichtbarkeit und keine HTTPS-Verschlüsselung - mit einer modernen Seite würden Sie deutlich mehr Implantat-Patienten erreichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Pötscher</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Linz</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ordination-poetscher.at/</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>+43 732 71 77 71</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only website at Hauserstraße 12, 4040 Linz. No SSL security and minimal web presence. No online booking system.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website wird ohne SSL-Verschlüsselung ausgeliefert - moderne Browser warnen Besucher mit 'Nicht sicher' direkt in der Adressleiste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Alexander Duffek</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Alexander Duffek</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Traun</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>http://www.zahnarzttraun.at/</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only website for a practice in the heart of Traun. No SSL, no online booking, basic informational layout.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Ordination im Zentrum von Traun verdient eine sichere, moderne Website mit Online-Terminanfrage statt der aktuellen unverschlüsselten Seite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Christian Brunner</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Christian Brunner</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Schörfling am Attersee</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>http://www.zahnarztbrunner.at/</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>zahnarzt.brunner@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>+43 6229 3856</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and Gmail business address</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only website. Uses a personal Gmail address for the practice. Limited opening days (Tue/Wed/Thu). Multilingual patient base (German/English/Hungarian) but no professional infrastructure.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Eine professionelle Praxis-Email statt einer Gmail-Adresse und eine sichere mehrsprachige Website würden bei Ihrer internationalen Patientenschaft sofort mehr Vertrauen schaffen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Walcher</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Walcher</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ordination-walcher.at/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only practice in Salzburg-Gneis (all insurances, free parking). No SSL encryption, minimal content, no online booking.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website läuft ohne HTTPS - das schreckt Patienten ab und wird von Google im Ranking abgewertet. Ein sicherer Neuauftritt ist schnell umgesetzt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Maximilian Negrin</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Maximilian Negrin</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>http://www.dr-negrin.at/</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and SSL certificate mismatch</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Practice founded in 1980. HTTP-only site with an SSL certificate mismatch error that makes the site unreachable for many browsers. Effectively invisible to security-conscious patients.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website ist wegen eines Zertifikatfehlers für viele Besucher gar nicht erreichbar - potenzielle Neupatienten landen auf einer Fehlerseite statt bei Ihnen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Innsmile</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>http://www.innsmile.at/</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>praxis@innsmile.at</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>+43 512 573511</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and broken template</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only single-page site that still shows 'Edit Content' placeholder text from the page builder. Very limited info, restricted phone hours (Mon-Fri 9-12). No online booking.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Auf Ihrer Startseite ist noch 'Edit Content'-Platzhaltertext sichtbar und die Seite läuft ohne HTTPS - das wirkt unfertig und sollte dringend professionell gelöst werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Helmut Ehrmann</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Helmut Ehrmann</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>http://dr-ehrmann.at/</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only website for a central practice in Bürgerstraße, Innsbruck. No SSL, basic layout, no online booking.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Ihre zentrale Lage in der Bürgerstraße verdient eine sichere, moderne Website - aktuell läuft sie ohne HTTPS und ohne Online-Terminanfrage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Amodent Zahnaerzte</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>http://amodent.at/</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>+43 316 32 34 75</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS - SSL certificate mismatch</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only site at Leonhardstraße 56 with an SSL certificate error (cert issued for a1webhosting.at). Appointment requests only by phone. Friendly brand ('Wir lieben Zähne') let down by neglected hosting.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website zeigt einen SSL-Zertifikatfehler - Patienten sehen eine rote Sicherheitswarnung statt Ihres sympathischen 'Wir lieben Zähne'-Auftritts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Stefanie Mohadjer</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Stefanie Mohadjer</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zahnaerztin.st/</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Unusual .st domain and thin content</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>New barrier-free practice at Kaiser-Josef-Platz, Graz-St. Leonhard. Uses an unusual .st domain. Site is thin on content and lacks modern trust elements or an online booking system.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Ihre neue barrierefreie Ordination ist ein starkes Verkaufsargument - eine moderne Website mit Teamfotos und Online-Terminanfrage würde das viel besser transportieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Koerner</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Koerner</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>http://dr-koerner.at/</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only website focused on aesthetic dentistry and oral surgery. No SSL security despite handling sensitive enquiries. No online booking.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website für ästhetische Zahnheilkunde läuft ohne SSL - gerade bei Premium-Leistungen erwarten Patienten eine sichere und hochwertige Online-Präsenz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Zahnarzt Dr. Moro</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Moro</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>http://zahnarzt-moro.at/</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and very low visibility</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only site with very low estimated traffic. Minimal online presence for a Klagenfurt practice. No online booking.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website hat minimale Online-Sichtbarkeit und keine HTTPS-Verschlüsselung - mit moderner SEO und sicherem Auftritt erreichen Sie deutlich mehr Klagenfurter Patienten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DesignYourSmile</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Matthias Gabriel / DDr. Astrid Fiedler</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>http://designyoursmile.at/</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>+43 463 511</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS for premium implant practice</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only site for an implantology and aesthetic practice specialising in anxiety patients. No SSL despite sensitive subject matter. Premium positioning undermined by insecure, dated site.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Als Praxis für Implantologie und Angstpatienten brauchen Sie eine besonders vertrauenswürdige Website - aktuell fehlt sogar die HTTPS-Verschlüsselung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Tamara Hanser</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Tamara Hanser</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>http://dr-hanser.com/</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS and images from 2012</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only site whose source still references images uploaded in 2012 (/wp-content/uploads/2012/09/). Strong indicator the site has not been updated in over a decade. No online booking.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website nutzt noch Bilder aus dem Jahr 2012 und läuft ohne HTTPS - ein kompletter Neuaufbau würde Ihre Praxis endlich zeitgemäß präsentieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Zahnregulierung Klagenfurt</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://zahnregulierung-klagenfurt.at/</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Very low visibility orthodontics site</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Orthodontics site with very low estimated traffic and minimal online presence. No before/after galleries or online booking to convert visitors.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Eine moderne Website mit Vorher-Nachher-Galerien und Online-Terminanfrage würde Ihre Zahnregulierungs-Praxis in Klagenfurt deutlich sichtbarer machen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DentBlanche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Simone Engel</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Villach</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dentblanche.at/</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Dated design across multi-location practice</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Covers Villach, Klagenfurt, Pörtschach and Feldkirchen with a focus on anxiety patients and treatment under anaesthesia. Strong regional reach but dated design and no clear online booking.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Ihre breite Abdeckung in Kärnten und der Fokus auf Angstpatienten sind starke Argumente - eine moderne Website wuerde diese USPs viel ueberzeugender kommunizieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Eberwein-Lach</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Eberwein-Lach</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Koettmannsdorf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>https://dr-eberwein.at/</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Minimal rural practice site</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Very thin web presence - little more than the address (9071 Köttmannsdorf) is visible. No online booking and few trust elements.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Ordination koennte mit einer modernen Website Patienten aus dem gesamten Raum Klagenfurt-Land ansprechen - aktuell ist online kaum Information vorhanden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Hotico</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Hotico</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Wien (1160)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://zahnarzt1160.weebly.com/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Free Weebly subdomain hosting</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Practice site hosted on a free Weebly subdomain (zahnarzt1160.weebly.com) instead of a custom domain. Patient reviews are positive but the free-builder URL signals a lack of professionalism.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Praxis ist auf einer kostenlosen Weebly-Adresse - eine eigene Domain mit professioneller Website wuerde die guten Patientenstimmen viel glaubwuerdiger praesentieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>prodent Wien-Hietzing</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Thomas Hartmann</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Wien (Hietzing)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>http://www.zahnarzt-hietzing.at/</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>No HTTPS in an affluent district</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>HTTP-only private practice in upscale Hietzing, founded 1982, with an international (English-speaking) patient base. No SSL and dated presentation for a premium catchment area.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Privatordination in Hietzing bedient auch internationale Patienten - eine sichere, mehrsprachige Website mit Online-Terminanfrage waere hier essenziell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Schwinner</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Schwinner</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Wien (1200)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zahnarzt-wien-1200.at/</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>praxis@zahnarzt-schwinner.at</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 332 42 88</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>No online booking and dated layout</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>All-insurances practice. Appointments only by phone ('Termin nur nach telefonischer Voranmeldung'). Dated layout, text-heavy, no online booking and few modern trust elements.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Patienten koennen Termine nur telefonisch vereinbaren - eine Online-Terminanfrage wuerde Anrufe reduzieren und auch ausserhalb der Oeffnungszeiten Buchungen ermoeglichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Edler Zahn</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Wien (1010)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edler-zahn.at/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 533 20 12</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Outdated site with encoding errors</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>All-insurances practice in the prime 1st district. Search snippets show character-encoding errors and the site appears unchanged since ~2021. Prime location underserved by a dated web presence.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website zeigt in den Google-Ergebnissen Zeichenfehler und wirkt veraltet - fuer eine Praxis im 1. Bezirk ein vermeidbarer Imageverlust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Thomas Hlawatsch</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>DDr. Thomas Hlawatsch</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Wiener Neustadt</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/ddr-thomas-hlawatsch/startseite</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>dr.t.hlawatsch@gmail.com</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>+43 2622 23409</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Free Google Sites page and Gmail address</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>The entire web presence is a free Google Sites page with a Gmail contact address. No custom domain, no design, no online booking - essentially a digital business card at Hauptplatz 34.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Praxis ist nur ueber eine kostenlose Google-Sites-Seite auffindbar - eine eigene Domain mit professioneller Website wuerde Sie in Wiener Neustadt klar von der Konkurrenz abheben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Ravnik</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Ravnik</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>St. Poelten</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://zahnarzt-ravnik.sta.io/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Free sta.io builder subdomain</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Website hosted on a free sta.io builder subdomain rather than a professional domain. Very minimal content, no online booking, no custom branding.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Praxis nutzt eine kostenlose Baukasten-Adresse (sta.io) - eine eigene professionelle Website wuerde Ihre Ordination deutlich serioeser wirken lassen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Kimberger Zahnarzt</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tulln</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://kimberger.com/</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Documented SEO problems</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Practice site (focus on anxiety patients) with documented SEO issues and no global ranking. Hard to find online despite a valuable niche. No clear online booking.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Spezialisierung auf Angstpatienten ist sehr gefragt - mit einer SEO-optimierten Website wuerden genau diese Patienten Sie online endlich finden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Zahnarzt-Pyhra</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Annika Plattner</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Pyhra</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://zahnarzt-pyhra.at/</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ordination@zahnarzt-pyhra.at</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Basic rural site without booking</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Small-town practice with a basic informational site. No online booking and limited modern features, though the rural setting means low competition.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Als Praxis in einer laendlichen Gemeinde koennten Sie mit einer modernen Website und Online-Terminanfrage einen echten Wettbewerbsvorteil schaffen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Bleaching Zahnaufhellung Vorarlberg</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Vorarlberg</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>https://bleaching-zahnaufhellung-vorarlberg.at/</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Single-service landing page</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Long, narrow domain covering only bleaching. Single-service landing page from 2023 with no comprehensive practice site behind it. Limited scope and trust elements.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Bleaching-Seite ist ein guter Einstieg - eine vollstaendige Praxis-Website wuerde Ihr gesamtes Leistungsspektrum zeigen und mehr Patienten gewinnen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Zahnarzt Fritz</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Vorarlberg</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zahnarzt-fritz.at/</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>+43 5557 2333</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Almost no content</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Extremely minimal site showing little more than a phone and fax number. No services, team or online booking presented to prospective patients.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Ihre Website zeigt praktisch nur die Telefonnummer - eine informative Praxis-Website wuerde Patienten von Ihrer Kompetenz ueberzeugen, bevor sie anrufen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Striessnig Bernd</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Bernd Striessnig</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Oberoesterreich</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.striessnig.net/</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>No online booking for a Bestellpraxis</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Runs as an appointment-only 'Bestellpraxis' to keep waiting times short, yet offers no online booking system - all scheduling is manual. Basic .net site.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Sie fuehren eine Bestellpraxis - ein Online-Buchungssystem wuerde Ihren Terminablauf automatisieren und Patienten die Vereinbarung rund um die Uhr ermoeglichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Zahnarzt Sixt</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Wilhelm Sixt</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Zell am Ziller</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zahnarztsixt.at/</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ordination@meddentzell.at</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>+43 5282 2174</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Phone/email booking only in a tourism region</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Practice in a busy Ziller valley ski-tourism area. Appointments only by phone or email - no online booking and no English version to capture holiday emergency patients.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>In einer Tourismusregion wie dem Zillertal koennten Sie mit mehrsprachiger Website und Online-Buchung auch Urlaubsgaeste als Notfallpatienten gewinnen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Zahnarzt Dr. Futter</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Matthias Futter</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>https://zahnarzt-dr-futter.com/</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>zahnarzt.futter@gmail.com</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>+43 699 15359188</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Gmail address and .com domain</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Uses a Gmail address and a .com (not .at) domain. Mobile-only phone number suggests a small operation with minimal digital infrastructure. Basic site from 2023.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Partially</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Eine professionelle Email-Adresse und eine .at-Domain wuerden bei oesterreichischen Patienten sofort mehr Vertrauen schaffen als die aktuelle Gmail-Loesung.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -518,67 +2759,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Practice Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Dentist Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Main Weakness</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Detailed Observation</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Online Booking</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Mobile Friendly</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Personalized Outreach Hook</t>
         </is>
@@ -1121,335 +3362,335 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Dr. Futter</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Dr. Matthias Futter</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Wien</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-dr-futter.com/</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>zahnarzt.futter@gmail.com</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>+43 699 15359188</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Gmail business email and basic site</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Using personal Gmail for professional practice. Mobile-only phone number suggests small practice. Basic website without modern features. Published 2023 but minimal web footprint.</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Die Verwendung einer Gmail-Adresse statt einer professionellen Praxis-Email wirkt nicht vertrauenswürdig – wir können das gemeinsam mit einem neuen Webauftritt lösen.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Edler Zahn Zahnarzt 1010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Wien (1010)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>https://www.edler-zahn.at/</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>+43 1 533 20 12</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Outdated presence and encoding issues</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Search snippet shows encoding issues (question mark characters). Tagline "Wir machen Ihre Zähne edler" suggests older marketing approach. Published date from 2021. Alle Kassen practice in prime 1st district location deserves better web presence.</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Ihre Website zeigt Zeichenkodierungsfehler in den Suchergebnissen – das vermittelt einen unprofessionellen Eindruck bei Google-Suchenden.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Dr. Lucian Petrascu</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Dr. Lucian Petrascu</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Graz</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-am-hauptplatz.at/</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Minimal web presence</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Very minimal search snippet - just "ZAHNARZTPRAXIS GRAZ Dr." No detailed content visible. Prime location (Hauptplatz) but minimal online presence. No apparent online booking or modern features.</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Ihre Praxis am Hauptplatz hat eine Top-Lage – aber Ihre Website spiegelt das nicht wider. Ein moderner Webauftritt würde mehr Laufkundschaft online anziehen.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt am Ring Baden</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Baden (NÖ)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>https://zahnarztamring.at/</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>info@zahnarztamring.at</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Basic web presence</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Published 2025 but minimal search presence. Only email visible in snippets. Baden bei Wien is affluent area where patients expect premium web experience.</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Ihre Praxis in der wohlhabenden Kurstadt Baden verdient einen Premium-Webauftritt der zu Ihrem Standort und Ihrer Klientel passt.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Dr. Masic-Redinger Zahnarzt</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Dr. Masic-Redinger</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Wien (1090)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>https://fmr-zahn.at/</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>No online booking and basic layout</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Website primarily shows Stornorichtlinien and address info. Recent address change suggests active practice. No visible online booking. Emphasis on phone scheduling and strict cancellation policy. Basic informational website.</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Ihre Website fokussiert auf Stornorichtlinien statt auf die Vorteile Ihrer Behandlung – ein einladender Webauftritt mit Online-Buchung würde mehr Neupatienten gewinnen.</t>
         </is>
@@ -1657,737 +3898,737 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Hallein Dr. Bachmayer</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Dr. Martha L. Bachmayer</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Hallein (Salzburg)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>https://www.zahnarzt-hallein.at/</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Basic wix/builder site</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Website appears to use page builder with map page as landing. ZFD - ÖZAK Implantologie certified but website doesn't reflect expertise level. Basic structure.</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Ihre Spezialisierung auf Implantologie verdient eine Website die Ihre Expertise und Zertifizierungen prominent präsentiert.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Dr. Roswitha Mayr</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Dr. Roswitha Mayr</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Steyr</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>https://www.zahnarztpraxis-steyr.at/</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>+43 7252 54045</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Outdated slider-based design</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Website uses outdated button-slider format typical of 2010-era design. Multiple generic service boxes. No online booking - calls for phone appointment. Text-heavy without modern visual hierarchy.</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Ihre Website nutzt ein veraltetes Slider-Design aus den 2010er Jahren – eine moderne Gestaltung würde Ihre umfangreichen Leistungen besser hervorheben.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>DDr. Matthias Mühlvenzl</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>DDr. Matthias Mühlvenzl</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Berndorf (NÖ)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-berndorf.at/</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>info@zahnarzt-berndorf.at</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Basic informational site</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Alle Kassen &amp; Privat practice. Basic website with opening hours and services listed. No online booking. Plain design without modern trust elements.</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Ihre Praxis bietet Alle Kassen und Privat – eine moderne Website mit Online-Terminbuchung würde beiden Patientengruppen entgegenkommen.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Dr. Ilona Bondar</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Dr. Ilona Bondar</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Graz</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>https://www.zahnarzt-bondar.at/</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>office@zahnarzt-bondar.at</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>+43 316 71 22 22</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Basic web presence without modern features</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Basic website with contact information. No apparent online booking system. Standard design without differentiating features.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Eine moderne Website mit Teamfotos und Patientenbewertungen würde Vertrauen aufbauen und Sie von anderen Grazer Praxen abheben.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Dr. med. dent. Christina Bergmüller</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Dr. Christina Bergmüller</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Salzburg</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>https://www.zahn-riedenburg.at/</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>ordination@zahn-riedenburg.at</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>+43 662 841 684</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Minimal website with cookie focus</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Search snippet dominated by cookie consent text rather than practice information. Minimal content visible. Leopoldskronstraße 4A/1B address in Salzburg.</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Der erste Eindruck Ihrer Website wird von einem Cookie-Banner dominiert – Patienten sollten sofort Ihre Leistungen und Ihr Team sehen.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>DDr. Karin Marcher &amp; Dr. Christian Marcher</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>DDr. Karin Marcher</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Gablitz (NÖ)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>https://www.marcher-zahnarzt.at/</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>office@marcher-zahnarzt.at</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>+43 2230 8940</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Comprehensive but outdated design</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Website has good content structure (Prophylaxe Ästhetische Zahnheilkunde Wurzelbehandlungen etc.) but design appears dated. Published 2023 suggesting recent update but still has older feel. No online booking visible.</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Ihre Website hat gute Inhalte aber das Design wirkt veraltet – ein modernes Redesign würde Ihre umfangreichen Leistungen zeitgemäß präsentieren.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Pyhra Dr. Plattner</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Dr. Annika Plattner</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Pyhra (NÖ)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-pyhra.at/</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>ordination@zahnarzt-pyhra.at</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Basic rural practice website</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Small-town dental practice with basic website. No apparent online booking. Rural location means less competition but also less awareness of modern web standards.</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Als Zahnarztpraxis in einer ländlichen Gemeinde können Sie mit einer modernen Website und Online-Terminbuchung einen echten Wettbewerbsvorteil schaffen.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Dr. Wiedemann &amp; Dr. Krnjic</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Dr. Wiedemann / Dr. Krnjic</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Salzburg</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>https://www.zahnwk.com/</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>+43 662 87 43 61</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Good content but older design approach</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Website has comprehensive content about services and philosophy. Long text blocks without modern visual hierarchy. Good practice description but could benefit from modern design and booking features.</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Ihre Praxis-Philosophie ist überzeugend beschrieben – ein modernes Design mit visueller Hierarchie würde diese Stärken noch besser zur Geltung bringen.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Fritz</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Vorarlberg</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>https://www.zahnarzt-fritz.at/</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>ordination@zahnarzt-fritz.at</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>+43 5557 2333</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Very minimal web presence</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Extremely minimal website with just phone number and fax visible. No modern features. Vorarlberg location.</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Ihre Website zeigt praktisch nur Ihre Telefonnummer – eine informative Praxis-Website würde Patienten von Ihrer Kompetenz überzeugen bevor sie anrufen.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Dr. Striessnig Bernd</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Dr. Bernd Striessnig</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Oberösterreich</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>https://www.striessnig.net/</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Basic Bestellpraxis website</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Uses .net domain (unusual for dental practice). Mentions Bestellpraxis (appointment-only) organization but no online booking system. Basic web presence.</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Sie betreiben eine Bestellpraxis – ein Online-Buchungssystem würde Ihren Workflow optimieren und Patienten die Terminvereinbarung erleichtern.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Dr. Eberwein-Lach</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Dr. Eberwein-Lach</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Köttmannsdorf (Kärnten)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>https://dr-eberwein.at/</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Minimal rural practice website</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Very minimal web presence. Only postal code 9071 Köttmannsdorf visible. Rural Kärnten location. No modern features apparent.</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Ihre ländliche Praxis könnte mit einer modernen Website Patienten aus der gesamten Region Klagenfurt-Land ansprechen.</t>
         </is>
@@ -2461,871 +4702,871 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Zahnmedizin Reindl</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Wien (1110)</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>https://zahnmedizin-reindl.at/</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Newer site but potential improvements</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Published 2025 - newer website. Wahlarzt practice in 1110 Wien. Describes modern environment. May already be adequate but could still benefit from optimization.</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Ihre moderne Praxisbeschreibung klingt vielversprechend – eine Optimierung der Online-Terminbuchung könnte noch mehr Wahlpatienten anziehen.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Zahnarzt Mallinger</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Wien (1150)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>https://zahnarzt-mallinger.at/</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Adequate but improvable</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Published 2025 - relatively new. Describes modern technologies. 15th district location. Could still benefit from enhanced features.</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Ihr Fokus auf fortschrittliche Technologien sollte sich auch in einem technologisch führenden Webauftritt widerspiegeln.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Dr. Golestani</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Dr. Sima Sylvia Golestani</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Wien (1120)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>https://zahnarzt-golestani.at/</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Functional but basic</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Published 2025 - newer site. Mentions Umbau (renovation). Alle Kassen practice. Functional but could benefit from modern features.</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Nach Ihrem Praxis-Umbau wäre auch ein frischer Webauftritt der ideale nächste Schritt um neue Patienten anzusprechen.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>DDr. Barbara &amp; Dr. Christian Krempl</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>DDr. Barbara Krempl</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Köflach (Steiermark)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>https://www.drkrempl.at/</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Basic dual-practice website</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Dual-location practice (Köflach). Published 2025. Basic web presence that could benefit from modern features and online booking.</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Als Praxis mit zwei Standorten könnten Sie mit einer modernen Website und zentralem Buchungssystem beide Ordinationen effizient verwalten.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Dr. Minihold Zahnarztpraxis</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Dr. Minihold</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Mödling (NÖ)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>https://www.minihold.at/</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Content marketing but older design</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Active content marketing (TV appearances with Christine Reiler). Published 2025. Has good content but design may be dated.</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>Ihre Medienpräsenz mit Christine Reiler ist beeindruckend – eine moderne Website würde diese Autorität noch besser transportieren.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Sixt</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Zell am Ziller (Tirol)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>https://www.zahnarztsixt.at/</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>ordination@meddentzell.at</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>+43 5282 2174</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Basic rural Tirol website</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Rural Tirol dental practice. Basic web presence. Published 2025 but functionality unclear. No apparent online booking for tourist/ski area.</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>In einer Tourismusregion wie Zell am Ziller könnten Sie mit mehrsprachiger Website und Online-Buchung auch Urlaubsgäste als Notfall-Patienten gewinnen.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Ordination Arzl</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Innsbruck (Arzl)</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>https://www.ordination-arzl.at/</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>hg@ordination-arzl.at</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>+43 512 265 938</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Basic practice website</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Published 2025. Basic ordination website in Innsbruck-Arzl district. Contact info visible but no modern features apparent.</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>Ihre Ordination in Arzl könnte mit einer modernen Website und klarer Leistungsübersicht mehr Patienten aus dem wachsenden Stadtteil gewinnen.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Zahnarzt Linz Mozartkreuzung</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Linz</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>https://www.zahnarztlinz.com/</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>+43 732 77 24 65</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Claims modern but basic web presence</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Website claims TOP MODERN Ordination. Alle Kassen und Privat. Central location. Has basic structure but may lack advanced features.</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Sie beschreiben Ihre Ordination als top modern – Ihre Website sollte diesen Anspruch mit einem ebenso modernen Design untermauern.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Dr. Susanne Pultar &amp; Johannes Pultar</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Dr. Susanne Pultar / Johannes Pultar</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Wien</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>https://www.zahnarzt-pultar.wien/</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>ordination@zahnarzt-pultar.wien</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>+43 1 50 54 128</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Has online booking - lower priority</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Published 2025. Mentions online booking option. Professional .wien domain. Already has some modern features.</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Ihre professionelle .wien-Domain und Online-Buchung sind bereits gut – eine Design-Optimierung könnte die Conversion-Rate weiter steigern.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Postolovska</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Wien (1220)</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>https://postolovska.at/</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Basic Donaustadt practice</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Published 2024. Basic website for 1220 Wien practice. Mentions emergency care. Growing district with many new residents looking online for dentists.</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>In der wachsenden Donaustadt suchen tausende neue Bewohner online nach einem Zahnarzt – eine optimierte Website mit starkem SEO wäre Gold wert.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Dr. Dolezal</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Dr. Dolezal</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Wien</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>https://dr-dolezal.com/</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Basic presence for implantology specialist</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Implantology specialist with Zahnärztekammer certification. .com domain instead of .at. Basic web presence that doesn't highlight specialization enough.</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Ihre Implantologie-Spezialisierung verdient eine Website die Ihre Expertise mit Vorher-Nachher-Bildern und Patientenstimmen unterstreicht.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Zahnspange Mödling Dr. Arnold</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Dr. Mariella Arnold</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Mödling (NÖ)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>https://www.zahnspange-moedling.at/</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>praxis@zahnspange-moedling.at</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>+43 2236 86 91 45</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Orthodontics-focused but could improve</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>Has 3D scanner mentioned. Orthodontics specialist. Website has some modern elements but could be enhanced.</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Ihre 3D-Scanner-Technologie ist ein starkes Differenzierungsmerkmal – eine moderne Website mit interaktiven Vorher-Nachher-Vergleichen würde das noch besser vermitteln.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>DentBlanche Dr. Engel</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Dr. Simone Engel</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Velden/Villach (Kärnten)</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>https://www.dentblanche.at/</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Multi-location but basic design</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Covers Villach/Klagenfurt/Pörtschach/Feldkirchen area. Focus on Angstpatienten and Narkosebehandlung. Has broad reach but website design unclear.</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Ihre breite regionale Abdeckung in Kärnten und Ihr Fokus auf Angstpatienten sind starke USPs – eine moderne Website könnte diese viel besser kommunizieren.</t>
         </is>
@@ -3399,67 +5640,67 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Bleaching Vorarlberg</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Vorarlberg</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>https://bleaching-zahnaufhellung-vorarlberg.at/</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>Single-service landing page from 2023</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Published 2023. Single-service focused website (bleaching only). Long domain name. Could be part of larger practice needing comprehensive website.</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Ihre Bleaching-Spezialseite ist ein guter Anfang – eine umfassende Praxis-Website würde Ihr gesamtes Leistungsspektrum präsentieren.</t>
         </is>
@@ -3600,881 +5841,471 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Zahnregulierung Klagenfurt</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Klagenfurt</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>https://zahnregulierung-klagenfurt.at/</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Low-traffic basic orthodontics site</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>Very low estimated traffic and value. Basic orthodontics website in Klagenfurt. Minimal online presence.</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>Ihre Zahnregulierungs-Praxis könnte mit modernem Webdesign und Vorher-Nachher-Galerien viel mehr Patienten in Klagenfurt ansprechen.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>DrKohlmaier Zahnärztin</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Dr. Barbara Cijan-Kohlmaier</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Klagenfurt</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>https://drkohlmaier.at/</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Basic presence for anxiety-friendly practice</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Focus on comfortable dental experience. Moderate traffic. Could benefit from enhanced trust elements and online booking.</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>Ihr Fokus auf entspanntes Zahnarzt-Erlebnis ist ein tolles Alleinstellungsmerkmal – eine beruhigende moderne Website würde dieses Versprechen visuell unterstützen.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Dr. Luka Baltic</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Dr. Luka Baltic</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Graz</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>https://drbaltic.at/</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>Cookie-consent dominated experience</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>Search experience dominated by cookie/privacy consent text rather than practice content. Modern dental practice but web presence doesn't reflect it well.</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>Der erste Eindruck Ihrer Website ist ein Cookie-Banner statt Ihrer Praxis – eine optimierte Website würde sofort Vertrauen und Kompetenz vermitteln.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt Dr. Futter Wien</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Dr. Matthias Futter</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Wien (Floridsdorf)</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-dr-futter.com/</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>zahnarzt.futter@gmail.com</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>+43 699 15359188</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Gmail email and .com domain</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Uses Gmail for professional communication and .com domain instead of .at. Published 2023. Mobile number only. Suggests small practice with minimal digital infrastructure.</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>Eine professionelle Email-Adresse und ein .at-Domain würden sofort mehr Vertrauen bei österreichischen Patienten schaffen.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Ordination Dr. Nidetzky</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Dr. Alexander Nidetzky</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Wien</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>Limited online hours and basic presence</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Found via Waze listing only. Very limited opening hours (Thursday 10-16). Basic online presence without dedicated modern website.</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>Eine eigene moderne Praxis-Website würde Ihre Ordination auch außerhalb der begrenzten Öffnungszeiten für Patienten sichtbar machen.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Kimberger Zahnarzt</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Not listed</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Tulln/Neulengbach (NÖ)</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>https://kimberger.com/</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>SEO issues and basic site</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Website has noted SEO issues. Focus on Angstpatienten (dental anxiety). Tulln/Neulengbach area in NÖ.</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>Ihre Spezialisierung auf Angstpatienten ist ein wertvolles Alleinstellungsmerkmal – eine SEO-optimierte Website würde genau diese Zielgruppe online erreichen.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Dr. Kremsner Zahnarzt Tulln</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Dr. Alexander Kremsner</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Tulln (NÖ)</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>https://zahnarzt-tulln.at/</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>Basic Austrian dental practice site</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>Zahnarzt in Tulln an der Donau. Zahn- Mund- und Kieferheilkunde. Basic web presence for medium-sized town.</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Partially</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>Als Zahnarzt in der wachsenden Donaustadt Tulln könnten Sie mit einer modernen Website die steigende Zahl neuer Einwohner ansprechen.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Practice Name</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Main Weakness</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Outreach Hook</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Amodent Zahnärzte</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Graz</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>No HTTPS - SSL certificate mismatch</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>http://amodent.at/</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website zeigt einen Sicherheitsfehler (SSL-Zertifikat stimmt nicht überein) – das schreckt potenzielle Patienten ab und wird von Google abgestraft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Ordination Dr. Walcher</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Salzburg</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>No HTTPS and minimal web presence</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>http://www.ordination-walcher.at/</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website läuft ohne HTTPS-Verschlüsselung – Google markiert sie als "nicht sicher" und Patienten verlieren Vertrauen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>DDr. Heinz-Dieter Müller</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Linz</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>No HTTPS and very basic presence</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>http://zahnarzt-mueller-linz.at/</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website hat keine SSL-Verschlüsselung und wirkt sehr minimalistisch – eine moderne Praxis-Website mit Online-Terminbuchung könnte Ihre Patientenakquise deutlich verbessern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Maximilian Negrin</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Innsbruck</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>No HTTPS with SSL cert mismatch</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>http://www.dr-negrin.at/</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website ist aufgrund eines SSL-Zertifikatfehlers für viele Browser nicht erreichbar – potenzielle Neupatienten können Ihre Seite nicht aufrufen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Hotico Zahnarzt 1160</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Wien</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Free Weebly hosting - extremely unprofessional</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>https://zahnarzt1160.weebly.com/</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Praxis-Website ist auf der kostenlosen Weebly-Plattform gehostet – ein eigener professioneller Webauftritt würde deutlich mehr Vertrauen schaffen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Innsmile Zahnarzt</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Innsbruck</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>No HTTPS and outdated single-page design</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>http://www.innsmile.at/</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website zeigt "Edit Content"-Text und läuft ohne SSL – ein professioneller Neuauftritt würde Ihre moderne Praxis besser repräsentieren.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Ravnik Zahnarzt</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>St. Pölten area</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Free sta.io builder platform</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>https://zahnarzt-ravnik.sta.io/</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Praxis nutzt eine kostenlose Website-Plattform (sta.io) – eine eigene professionelle Website würde Ihre Praxis viel besser repräsentieren.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Tamara Hanser</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Kärnten</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>HTTP only and dated image references</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>http://dr-hanser.com/</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website enthält Bildreferenzen aus 2012 und läuft ohne HTTPS – ein kompletter Neuaufbau würde Ihre Praxis zeitgemäß präsentieren.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Körner Zahnarzt</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Klagenfurt</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>HTTP only website</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>http://dr-koerner.at/</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Ihre Website für ästhetische Zahnheilkunde läuft ohne SSL-Verschlüsselung – gerade bei Premium-Leistungen erwarten Patienten eine sichere, moderne Website.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>DesignYourSmile Klagenfurt</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Klagenfurt</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>HTTP only for aesthetic dentistry practice</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>http://designyoursmile.at/</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Als Praxis für Angstpatienten und Implantologie brauchen Sie eine vertrauenswürdige, sichere Website – HTTPS und modernes Design sind dabei essentiell.</t>
         </is>
       </c>
     </row>
@@ -4502,37 +6333,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Practice Name</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Main Weakness</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Outreach Hook</t>
         </is>
@@ -4894,6 +6725,416 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Practice Name</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Main Weakness</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Outreach Hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Amodent Zahnärzte</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>No HTTPS - SSL certificate mismatch</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>http://amodent.at/</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website zeigt einen Sicherheitsfehler (SSL-Zertifikat stimmt nicht überein) – das schreckt potenzielle Patienten ab und wird von Google abgestraft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Ordination Dr. Walcher</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>No HTTPS and minimal web presence</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>http://www.ordination-walcher.at/</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website läuft ohne HTTPS-Verschlüsselung – Google markiert sie als "nicht sicher" und Patienten verlieren Vertrauen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>DDr. Heinz-Dieter Müller</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Linz</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>No HTTPS and very basic presence</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>http://zahnarzt-mueller-linz.at/</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website hat keine SSL-Verschlüsselung und wirkt sehr minimalistisch – eine moderne Praxis-Website mit Online-Terminbuchung könnte Ihre Patientenakquise deutlich verbessern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Maximilian Negrin</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>No HTTPS with SSL cert mismatch</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>http://www.dr-negrin.at/</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website ist aufgrund eines SSL-Zertifikatfehlers für viele Browser nicht erreichbar – potenzielle Neupatienten können Ihre Seite nicht aufrufen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Hotico Zahnarzt 1160</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Free Weebly hosting - extremely unprofessional</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>https://zahnarzt1160.weebly.com/</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Praxis-Website ist auf der kostenlosen Weebly-Plattform gehostet – ein eigener professioneller Webauftritt würde deutlich mehr Vertrauen schaffen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Innsmile Zahnarzt</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>No HTTPS and outdated single-page design</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>http://www.innsmile.at/</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website zeigt "Edit Content"-Text und läuft ohne SSL – ein professioneller Neuauftritt würde Ihre moderne Praxis besser repräsentieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Ravnik Zahnarzt</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>St. Pölten area</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Free sta.io builder platform</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>https://zahnarzt-ravnik.sta.io/</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Praxis nutzt eine kostenlose Website-Plattform (sta.io) – eine eigene professionelle Website würde Ihre Praxis viel besser repräsentieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Tamara Hanser</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Kärnten</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>HTTP only and dated image references</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>http://dr-hanser.com/</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website enthält Bildreferenzen aus 2012 und läuft ohne HTTPS – ein kompletter Neuaufbau würde Ihre Praxis zeitgemäß präsentieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Körner Zahnarzt</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>HTTP only website</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>http://dr-koerner.at/</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Ihre Website für ästhetische Zahnheilkunde läuft ohne SSL-Verschlüsselung – gerade bei Premium-Leistungen erwarten Patienten eine sichere, moderne Website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>DesignYourSmile Klagenfurt</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Klagenfurt</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>HTTP only for aesthetic dentistry practice</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>http://designyoursmile.at/</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Als Praxis für Angstpatienten und Implantologie brauchen Sie eine vertrauenswürdige, sichere Website – HTTPS und modernes Design sind dabei essentiell.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
